--- a/Optimizacion/Resultados 100.000 L/Resultados 100.000 L.xlsx
+++ b/Optimizacion/Resultados 100.000 L/Resultados 100.000 L.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\p-mfolch\Documents\Proyecto_Tintos_CyT\Optimizacion\Resultados 100.000 L\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5331C6BB-5F16-407E-8731-14BAF6435F23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09982FA5-69F6-4A77-9537-75DF4C9B4F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{C2B462DC-C29F-43F6-8EBA-ACE5CEA212F8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{C2B462DC-C29F-43F6-8EBA-ACE5CEA212F8}"/>
   </bookViews>
   <sheets>
     <sheet name="DATOS 100.000 L" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="60">
   <si>
     <t>Data CA 25 F.N. estanque 68.xlsx</t>
   </si>
@@ -202,13 +202,28 @@
   </si>
   <si>
     <t>Data CS 24 BOLDO estanque 30.xlsx</t>
+  </si>
+  <si>
+    <t>Agregué división por n de fermentaciones</t>
+  </si>
+  <si>
+    <t>2.a</t>
+  </si>
+  <si>
+    <t>2.b</t>
+  </si>
+  <si>
+    <t>2.c</t>
+  </si>
+  <si>
+    <t>2.d</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="0.0000000"/>
     <numFmt numFmtId="165" formatCode="#,##0.00000000"/>
     <numFmt numFmtId="166" formatCode="#,##0.000000000"/>
@@ -216,6 +231,7 @@
     <numFmt numFmtId="168" formatCode="0.000000000"/>
     <numFmt numFmtId="169" formatCode="0.000000"/>
     <numFmt numFmtId="170" formatCode="0.0%"/>
+    <numFmt numFmtId="171" formatCode="0.000%"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -254,7 +270,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -279,6 +295,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="20">
     <border>
@@ -529,7 +551,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -548,7 +570,6 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -580,6 +601,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="171" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -885,7 +916,7 @@
       </c>
       <c r="D2">
         <f ca="1">RANDBETWEEN(1,16)</f>
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -911,16 +942,16 @@
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="26">
         <v>13</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="27">
         <v>4</v>
       </c>
     </row>
@@ -928,14 +959,14 @@
       <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="29"/>
+      <c r="C6" s="28"/>
       <c r="D6">
         <v>4</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="29">
         <v>8</v>
       </c>
     </row>
@@ -943,14 +974,14 @@
       <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="29"/>
+      <c r="C7" s="28"/>
       <c r="D7">
         <v>8</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="29">
         <v>13</v>
       </c>
     </row>
@@ -958,14 +989,14 @@
       <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="31"/>
-      <c r="D8" s="32">
+      <c r="C8" s="30"/>
+      <c r="D8" s="31">
         <v>14</v>
       </c>
-      <c r="E8" s="33">
+      <c r="E8" s="32">
         <v>14</v>
       </c>
     </row>
@@ -973,16 +1004,16 @@
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="26">
         <v>12</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="27">
         <v>1</v>
       </c>
     </row>
@@ -990,14 +1021,14 @@
       <c r="A10" s="6">
         <v>9</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="29"/>
+      <c r="C10" s="28"/>
       <c r="D10">
         <v>6</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="29">
         <v>6</v>
       </c>
     </row>
@@ -1005,14 +1036,14 @@
       <c r="A11" s="4">
         <v>10</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="29"/>
+      <c r="C11" s="28"/>
       <c r="D11">
         <v>9</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="29">
         <v>9</v>
       </c>
     </row>
@@ -1020,14 +1051,14 @@
       <c r="A12" s="4">
         <v>11</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="31"/>
-      <c r="D12" s="32">
+      <c r="C12" s="30"/>
+      <c r="D12" s="31">
         <v>1</v>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="32">
         <v>12</v>
       </c>
     </row>
@@ -1038,13 +1069,13 @@
       <c r="B13" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="26">
         <v>3</v>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="27">
         <v>3</v>
       </c>
     </row>
@@ -1055,11 +1086,11 @@
       <c r="B14" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="29"/>
+      <c r="C14" s="28"/>
       <c r="D14">
         <v>15</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="29">
         <v>8</v>
       </c>
     </row>
@@ -1070,11 +1101,11 @@
       <c r="B15" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C15" s="29"/>
+      <c r="C15" s="28"/>
       <c r="D15">
         <v>8</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="29">
         <v>12</v>
       </c>
     </row>
@@ -1085,11 +1116,11 @@
       <c r="B16" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C16" s="31"/>
-      <c r="D16" s="32">
+      <c r="C16" s="30"/>
+      <c r="D16" s="31">
         <v>12</v>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="32">
         <v>15</v>
       </c>
     </row>
@@ -1100,40 +1131,40 @@
       <c r="B17" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="26">
         <v>16</v>
       </c>
-      <c r="E17" s="28">
+      <c r="E17" s="27">
         <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C18" s="29"/>
+      <c r="C18" s="28"/>
       <c r="D18">
         <v>11</v>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="29">
         <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C19" s="29"/>
+      <c r="C19" s="28"/>
       <c r="D19">
         <v>4</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="29">
         <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C20" s="31"/>
-      <c r="D20" s="32">
+      <c r="C20" s="30"/>
+      <c r="D20" s="31">
         <v>14</v>
       </c>
-      <c r="E20" s="33">
+      <c r="E20" s="32">
         <v>16</v>
       </c>
     </row>
@@ -1145,7 +1176,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B186DA4B-EAD9-4D2D-A868-4303C49D66B8}">
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AD11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
@@ -1162,94 +1193,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" s="8" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="I1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="J1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="L1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="M1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="N1" s="15" t="s">
+      <c r="N1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="O1" s="18" t="s">
+      <c r="O1" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="P1" s="18" t="s">
+      <c r="P1" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="Q1" s="19" t="s">
+      <c r="Q1" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="R1" s="19" t="s">
+      <c r="R1" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="19" t="s">
+      <c r="S1" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="T1" s="20" t="s">
+      <c r="T1" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="U1" s="20" t="s">
+      <c r="U1" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="V1" s="20" t="s">
+      <c r="V1" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="W1" s="20" t="s">
+      <c r="W1" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="X1" s="20" t="s">
+      <c r="X1" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="Y1" s="20" t="s">
+      <c r="Y1" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="Z1" s="19" t="s">
+      <c r="Z1" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="AA1" s="19" t="s">
+      <c r="AA1" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="AB1" s="21" t="s">
+      <c r="AB1" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="AC1" s="19" t="s">
+      <c r="AC1" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="AD1" s="19" t="s">
+      <c r="AD1" s="18" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1275,7 +1306,7 @@
       <c r="G2" s="9">
         <v>0.5</v>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="21">
         <v>0.01</v>
       </c>
       <c r="I2" s="9">
@@ -1293,7 +1324,7 @@
       <c r="M2" s="9">
         <v>2.1388999999999998E-2</v>
       </c>
-      <c r="N2" s="16">
+      <c r="N2" s="15">
         <f>SUM(J2:M2)</f>
         <v>0.30066000000000004</v>
       </c>
@@ -1370,7 +1401,7 @@
       <c r="G3" s="9">
         <v>0.5</v>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="21">
         <v>1E-3</v>
       </c>
       <c r="I3" s="9"/>
@@ -1378,7 +1409,7 @@
       <c r="K3" s="9"/>
       <c r="L3" s="9"/>
       <c r="M3" s="9"/>
-      <c r="N3" s="16">
+      <c r="N3" s="15">
         <f t="shared" ref="N3:N5" si="0">SUM(J3:M3)</f>
         <v>0</v>
       </c>
@@ -1399,193 +1430,193 @@
       <c r="AC3" s="9"/>
       <c r="AD3" s="9"/>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A4" s="9">
-        <v>2</v>
-      </c>
-      <c r="B4" s="9" t="s">
+    <row r="4" spans="1:30" s="41" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="33">
         <v>1000</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="33">
         <v>25</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="33">
         <v>1.5</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="33">
         <v>1.5</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="33">
         <v>0.5</v>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="34">
         <v>0.01</v>
       </c>
-      <c r="I4" s="9">
+      <c r="I4" s="33">
         <v>0.40002406336472002</v>
       </c>
-      <c r="J4" s="9">
+      <c r="J4" s="33">
         <v>9.5919999999999998E-3</v>
       </c>
-      <c r="K4" s="9">
+      <c r="K4" s="33">
         <v>0.163324</v>
       </c>
-      <c r="L4" s="9">
+      <c r="L4" s="33">
         <v>0.13736400000000001</v>
       </c>
-      <c r="M4" s="9">
+      <c r="M4" s="33">
         <v>9.6762000000000001E-2</v>
       </c>
-      <c r="N4" s="16">
+      <c r="N4" s="35">
         <f t="shared" si="0"/>
         <v>0.40704200000000001</v>
       </c>
-      <c r="O4" s="9">
+      <c r="O4" s="33">
         <f>24*60+12.47</f>
         <v>1452.47</v>
       </c>
-      <c r="P4" s="13">
+      <c r="P4" s="36">
         <f>O4/60</f>
         <v>24.207833333333333</v>
       </c>
-      <c r="Q4" s="9">
+      <c r="Q4" s="33">
         <v>0.26206656979687798</v>
       </c>
-      <c r="R4" s="10">
+      <c r="R4" s="37">
         <v>3.6655090274713298</v>
       </c>
-      <c r="S4" s="10">
+      <c r="S4" s="37">
         <v>5.0374474105710503</v>
       </c>
-      <c r="T4" s="11">
+      <c r="T4" s="38">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="U4" s="11">
+      <c r="U4" s="38">
         <v>8.5518540000000005</v>
       </c>
-      <c r="V4" s="11">
+      <c r="V4" s="38">
         <v>7.1656500000000003</v>
       </c>
-      <c r="W4" s="11">
+      <c r="W4" s="38">
         <v>44.150669999999998</v>
       </c>
-      <c r="X4" s="11">
+      <c r="X4" s="38">
         <v>42.528283999999999</v>
       </c>
-      <c r="Y4" s="11">
+      <c r="Y4" s="38">
         <v>1E-4</v>
       </c>
-      <c r="Z4" s="14">
+      <c r="Z4" s="39">
         <v>0.97485643145817502</v>
       </c>
-      <c r="AA4" s="12">
+      <c r="AA4" s="40">
         <v>5.2665504281965596</v>
       </c>
-      <c r="AB4" s="11">
+      <c r="AB4" s="38">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AC4" s="9">
+      <c r="AC4" s="33">
         <v>0.35589645773479001</v>
       </c>
-      <c r="AD4" s="9">
+      <c r="AD4" s="33">
         <v>0.52196650894014596</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A5" s="9">
-        <v>2</v>
-      </c>
-      <c r="B5" s="9" t="s">
+    <row r="5" spans="1:30" s="41" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="33">
         <v>1000</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="33">
         <v>25</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="33">
         <v>1.5</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="33">
         <v>1.5</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="33">
         <v>0.5</v>
       </c>
-      <c r="H5" s="22">
+      <c r="H5" s="34">
         <v>1E-3</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="33">
         <v>0.35532146484654198</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="33">
         <v>3.8476000000000003E-2</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K5" s="33">
         <v>0.121822</v>
       </c>
-      <c r="L5" s="9">
+      <c r="L5" s="33">
         <v>6.7739999999999995E-2</v>
       </c>
-      <c r="M5" s="9">
+      <c r="M5" s="33">
         <v>0.100124</v>
       </c>
-      <c r="N5" s="16">
+      <c r="N5" s="35">
         <f t="shared" si="0"/>
         <v>0.32816200000000001</v>
       </c>
-      <c r="O5" s="9">
+      <c r="O5" s="33">
         <f>68*60+55.88</f>
         <v>4135.88</v>
       </c>
-      <c r="P5" s="13">
+      <c r="P5" s="36">
         <f>O5/60</f>
         <v>68.931333333333342</v>
       </c>
-      <c r="Q5" s="9">
+      <c r="Q5" s="33">
         <v>9.8049256361115805E-2</v>
       </c>
-      <c r="R5" s="10">
+      <c r="R5" s="37">
         <v>3.7642227106778101</v>
       </c>
-      <c r="S5" s="10">
+      <c r="S5" s="37">
         <v>5.0218297479588498</v>
       </c>
-      <c r="T5" s="11">
+      <c r="T5" s="38">
         <v>9.6469999999999993E-3</v>
       </c>
-      <c r="U5" s="11">
+      <c r="U5" s="38">
         <v>8.5518540000000005</v>
       </c>
-      <c r="V5" s="11">
+      <c r="V5" s="38">
         <v>7.1656500000000003</v>
       </c>
-      <c r="W5" s="11">
+      <c r="W5" s="38">
         <v>44.150669999999998</v>
       </c>
-      <c r="X5" s="11">
+      <c r="X5" s="38">
         <v>42.528283999999999</v>
       </c>
-      <c r="Y5" s="11">
+      <c r="Y5" s="38">
         <v>1E-4</v>
       </c>
-      <c r="Z5" s="12">
+      <c r="Z5" s="40">
         <v>1.0193069327270401</v>
       </c>
-      <c r="AA5" s="12">
+      <c r="AA5" s="40">
         <v>5.3714989362152199</v>
       </c>
-      <c r="AB5" s="11">
+      <c r="AB5" s="38">
         <v>1.6426339999999999</v>
       </c>
-      <c r="AC5" s="9">
+      <c r="AC5" s="33">
         <v>0.35813924314054002</v>
       </c>
-      <c r="AD5" s="9">
+      <c r="AD5" s="33">
         <v>0.48519944839122398</v>
       </c>
     </row>
@@ -1597,13 +1628,13 @@
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
-      <c r="H6" s="22"/>
+      <c r="H6" s="21"/>
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
       <c r="K6" s="9"/>
       <c r="L6" s="9"/>
       <c r="M6" s="9"/>
-      <c r="N6" s="16">
+      <c r="N6" s="15">
         <f>SUM(J6:M6)</f>
         <v>0</v>
       </c>
@@ -1624,6 +1655,258 @@
       <c r="AC6" s="9"/>
       <c r="AD6" s="9"/>
     </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="H9" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="I9" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="M9" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="N9" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="O9" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="P9" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q9" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="R9" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="S9" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="T9" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="U9" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="V9" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="W9" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="X9" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y9" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z9" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA9" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB9" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC9" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD9" s="18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" s="41" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="33">
+        <v>1000</v>
+      </c>
+      <c r="D10" s="33">
+        <v>25</v>
+      </c>
+      <c r="E10" s="33">
+        <v>1.5</v>
+      </c>
+      <c r="F10" s="33">
+        <v>1.5</v>
+      </c>
+      <c r="G10" s="33">
+        <v>0.5</v>
+      </c>
+      <c r="H10" s="34">
+        <v>0.01</v>
+      </c>
+      <c r="I10" s="33">
+        <v>3.33353386137267E-2</v>
+      </c>
+      <c r="J10" s="33"/>
+      <c r="K10" s="33"/>
+      <c r="L10" s="33"/>
+      <c r="M10" s="33"/>
+      <c r="N10" s="35">
+        <f t="shared" ref="N10" si="1">SUM(J10:M10)</f>
+        <v>0</v>
+      </c>
+      <c r="O10" s="33">
+        <f>25*60+48.13</f>
+        <v>1548.13</v>
+      </c>
+      <c r="P10" s="36">
+        <f>O10/60</f>
+        <v>25.802166666666668</v>
+      </c>
+      <c r="Q10" s="33">
+        <v>0.26206656979687798</v>
+      </c>
+      <c r="R10" s="37">
+        <v>3.6655090274713298</v>
+      </c>
+      <c r="S10" s="37">
+        <v>5.0374474105710503</v>
+      </c>
+      <c r="T10" s="38">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="U10" s="38">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="V10" s="38">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="W10" s="38">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="X10" s="38">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="Y10" s="38">
+        <v>1E-4</v>
+      </c>
+      <c r="Z10" s="39">
+        <v>0.97485643145817502</v>
+      </c>
+      <c r="AA10" s="40">
+        <v>5.2665504281965596</v>
+      </c>
+      <c r="AB10" s="38">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="AC10" s="33">
+        <v>0.35589645773479001</v>
+      </c>
+      <c r="AD10" s="33">
+        <v>0.52196650894014596</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" s="41" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="33">
+        <v>1000</v>
+      </c>
+      <c r="D11" s="33">
+        <v>25</v>
+      </c>
+      <c r="E11" s="33">
+        <v>1.5</v>
+      </c>
+      <c r="F11" s="33">
+        <v>1.5</v>
+      </c>
+      <c r="G11" s="33">
+        <v>0.5</v>
+      </c>
+      <c r="H11" s="42">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="I11" s="33"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="33"/>
+      <c r="L11" s="33"/>
+      <c r="M11" s="33"/>
+      <c r="N11" s="35">
+        <f t="shared" ref="N11" si="2">SUM(J11:M11)</f>
+        <v>0</v>
+      </c>
+      <c r="O11" s="33"/>
+      <c r="P11" s="36">
+        <f>O11/60</f>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="33"/>
+      <c r="R11" s="37"/>
+      <c r="S11" s="37"/>
+      <c r="T11" s="38">
+        <v>9.6469999999999993E-3</v>
+      </c>
+      <c r="U11" s="38">
+        <v>8.5518540000000005</v>
+      </c>
+      <c r="V11" s="38">
+        <v>7.1656500000000003</v>
+      </c>
+      <c r="W11" s="38">
+        <v>44.150669999999998</v>
+      </c>
+      <c r="X11" s="38">
+        <v>42.528283999999999</v>
+      </c>
+      <c r="Y11" s="38">
+        <v>1E-4</v>
+      </c>
+      <c r="Z11" s="39"/>
+      <c r="AA11" s="40"/>
+      <c r="AB11" s="38">
+        <v>1.6426339999999999</v>
+      </c>
+      <c r="AC11" s="33"/>
+      <c r="AD11" s="33"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
